--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484236_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484236_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3548</v>
+        <v>10.2924</v>
       </c>
       <c r="E2" t="n">
-        <v>11.5473</v>
+        <v>9.4032</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8075</v>
+        <v>0.8892</v>
       </c>
       <c r="G2" t="n">
         <v>4.6312</v>
@@ -610,13 +610,13 @@
         <v>0.7814</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9505</v>
+        <v>1.8881</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9649</v>
+        <v>1.8208</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0144</v>
+        <v>0.0673</v>
       </c>
       <c r="V2" t="n">
         <v>2.9917</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6023</v>
+        <v>8.0341</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6389</v>
+        <v>8.771100000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0366</v>
+        <v>-0.7371</v>
       </c>
       <c r="G3" t="n">
         <v>6.5727</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7165</v>
+        <v>0.7153</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4566</v>
+        <v>0.6756</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2598</v>
+        <v>0.0398</v>
       </c>
       <c r="V3" t="n">
         <v>0.9414</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7142</v>
+        <v>4.0725</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8155</v>
+        <v>6.0377</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1014</v>
+        <v>-1.9652</v>
       </c>
       <c r="G4" t="n">
         <v>3.5148</v>
@@ -766,13 +766,13 @@
         <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>0.044</v>
+        <v>0.4024</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0731</v>
+        <v>1.2953</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0291</v>
+        <v>-0.8929</v>
       </c>
       <c r="V4" t="n">
         <v>0.1554</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2496</v>
+        <v>1.8111</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4327</v>
+        <v>1.967</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1831</v>
+        <v>-0.1559</v>
       </c>
       <c r="G5" t="n">
         <v>3.0838</v>
@@ -844,13 +844,13 @@
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6317</v>
+        <v>0.1933</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4446</v>
+        <v>0.9789</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8129</v>
+        <v>-0.7857</v>
       </c>
       <c r="V5" t="n">
         <v>0.4875</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7183</v>
+        <v>1.1942</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3645</v>
+        <v>1.6534</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0828</v>
+        <v>-0.4592</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0166</v>
+        <v>1.6894</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7786999999999999</v>
+        <v>2.0537</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7953</v>
+        <v>-0.3644</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2103</v>
+        <v>1.6995</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1241</v>
+        <v>1.659</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3344</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1938</v>
+        <v>-0.0101</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.3948</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5391</v>
+        <v>-0.4049</v>
       </c>
       <c r="P6" t="n">
         <v>-0.1953</v>
@@ -922,28 +922,28 @@
         <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2884</v>
+        <v>1.0407</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3961</v>
+        <v>0.9307</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1077</v>
+        <v>0.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2186</v>
+        <v>-1.3405</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.3405</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3714</v>
+        <v>0.9853</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8851</v>
+        <v>-0.8796</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5137</v>
+        <v>1.8649</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6894</v>
+        <v>-0.0166</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0537</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3644</v>
+        <v>-0.7953</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6995</v>
+        <v>-1.2103</v>
       </c>
       <c r="K7" t="n">
-        <v>1.659</v>
+        <v>0.1241</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>-1.3344</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0101</v>
+        <v>1.1938</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3948</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4049</v>
+        <v>0.5391</v>
       </c>
       <c r="P7" t="n">
         <v>-0.1953</v>
@@ -1000,22 +1000,22 @@
         <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2179</v>
+        <v>-0.0214</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1624</v>
+        <v>0.0888</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0555</v>
+        <v>-0.1102</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3405</v>
+        <v>1.2186</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9979</v>
+        <v>-0.2024</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0529</v>
+        <v>0.7155</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.945</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0586</v>
@@ -1078,13 +1078,13 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9394</v>
+        <v>-0.1438</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3356</v>
+        <v>0.4327</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6038</v>
+        <v>-0.5765</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4568</v>
+        <v>-1.7675</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1056</v>
+        <v>-0.389</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3513</v>
+        <v>-1.3785</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3919</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0649</v>
+        <v>-0.3756</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1899</v>
+        <v>-0.0935</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2548</v>
+        <v>-0.2821</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3261</v>
+        <v>-3.0024</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3805</v>
+        <v>-1.8662</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9456</v>
+        <v>-1.1362</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6089</v>
@@ -1234,13 +1234,13 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3032</v>
+        <v>-0.9795</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4404</v>
+        <v>-0.0453</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7436</v>
+        <v>-0.9342</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.238</v>
+        <v>-3.9008</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7476</v>
+        <v>-2.4649</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4904</v>
+        <v>-1.436</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9709</v>
@@ -1312,13 +1312,13 @@
         <v>0.1953</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9266</v>
+        <v>-0.5895</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4566</v>
+        <v>-0.1739</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.47</v>
+        <v>-0.4155</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3405</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.1031</v>
+        <v>-7.1149</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.4042</v>
+        <v>-6.1709</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6989</v>
+        <v>-0.944</v>
       </c>
       <c r="G12" t="n">
         <v>-6.3072</v>
@@ -1390,13 +1390,13 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6973</v>
+        <v>0.2909</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4566</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2406</v>
+        <v>-0.4858</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1219</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.888699999999998</v>
+        <v>10.40160000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>15.2642</v>
+        <v>16.7773</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.3757</v>
+        <v>-6.375800000000001</v>
       </c>
       <c r="G13" t="n">
         <v>9.137800000000004</v>
@@ -1468,10 +1468,10 @@
         <v>9.767299999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9078000000000002</v>
+        <v>2.420899999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>5.1738</v>
+        <v>6.6868</v>
       </c>
       <c r="U13" t="n">
         <v>-4.2658</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.8263</v>
+        <v>5.7053</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7431</v>
+        <v>3.5186</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0832</v>
+        <v>2.1867</v>
       </c>
       <c r="G14" t="n">
         <v>1.9677</v>
@@ -1546,13 +1546,13 @@
         <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4996</v>
+        <v>2.3785</v>
       </c>
       <c r="T14" t="n">
-        <v>4.02</v>
+        <v>1.7954</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4796</v>
+        <v>0.5831</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3991</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4498</v>
+        <v>5.6009</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4192</v>
+        <v>6.3292</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9694</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>6.685</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7776</v>
+        <v>0.3735</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.773</v>
+        <v>0.137</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0046</v>
+        <v>0.2365</v>
       </c>
       <c r="V15" t="n">
         <v>0.8865</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0795</v>
+        <v>2.1755</v>
       </c>
       <c r="E16" t="n">
-        <v>5.4408</v>
+        <v>5.2386</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.3613</v>
+        <v>-3.0631</v>
       </c>
       <c r="G16" t="n">
         <v>0.2924</v>
@@ -1702,13 +1702,13 @@
         <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0175</v>
+        <v>0.0785</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0264</v>
+        <v>0.8242</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0439</v>
+        <v>-0.7457</v>
       </c>
       <c r="V16" t="n">
         <v>1.2186</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0299</v>
+        <v>-1.5446</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5811</v>
+        <v>-3.0873</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.6109</v>
+        <v>1.5427</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.6464</v>
+        <v>-2.4365</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.2812</v>
+        <v>-1.3313</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3652</v>
+        <v>-1.1052</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5696</v>
+        <v>-2.9511</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2802</v>
+        <v>-1.0374</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8498</v>
+        <v>-1.9137</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.216</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.001</v>
+        <v>-0.2939</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.215</v>
+        <v>0.8085</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9636</v>
+        <v>0.4045</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0114</v>
+        <v>0.2312</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0479</v>
+        <v>0.1732</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4959</v>
+        <v>0.4875</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2735</v>
+        <v>-1.5498</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6655</v>
+        <v>1.8733</v>
       </c>
       <c r="F18" t="n">
-        <v>0.392</v>
+        <v>-3.423</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5028</v>
+        <v>-2.6464</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.9878</v>
+        <v>-2.2812</v>
       </c>
       <c r="I18" t="n">
-        <v>0.485</v>
+        <v>-0.3652</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.5528</v>
+        <v>0.5696</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.6337</v>
+        <v>-0.2802</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>0.8498</v>
       </c>
       <c r="M18" t="n">
-        <v>0.05</v>
+        <v>-3.216</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.354</v>
+        <v>-2.001</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4041</v>
+        <v>-1.215</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.153</v>
+        <v>0.4437</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1127</v>
+        <v>1.3036</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0403</v>
+        <v>-0.8599</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3991</v>
+        <v>-1.4959</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3991</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8711</v>
+        <v>-2.2333</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3779</v>
+        <v>-2.8677</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4932</v>
+        <v>0.6344</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6059</v>
+        <v>-2.5028</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5674</v>
+        <v>-2.9878</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0385</v>
+        <v>0.485</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3077</v>
+        <v>-2.5528</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6741</v>
+        <v>-2.6337</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2982</v>
+        <v>0.05</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8933</v>
+        <v>-0.354</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4049</v>
+        <v>0.4041</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0614</v>
+        <v>-0.1128</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2888</v>
+        <v>-0.3149</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7726</v>
+        <v>0.2021</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2102</v>
+        <v>-0.3991</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0084</v>
+        <v>-0.3991</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0848</v>
+        <v>-2.5133</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.8962</v>
+        <v>-0.0746</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8114</v>
+        <v>-2.4387</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.4365</v>
+        <v>-2.6059</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3313</v>
+        <v>-1.5674</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1052</v>
+        <v>-1.0385</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.9511</v>
+        <v>-1.3077</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.0374</v>
+        <v>-0.6741</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9137</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5145999999999999</v>
+        <v>-1.2982</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2939</v>
+        <v>-0.8933</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8085</v>
+        <v>-0.4049</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1357</v>
+        <v>-0.7036</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5777</v>
+        <v>0.0145</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5581</v>
+        <v>-0.7181</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4875</v>
+        <v>0.2102</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1219</v>
+        <v>-1.0084</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6763</v>
+        <v>-5.3937</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1087</v>
+        <v>-1.9065</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.5676</v>
+        <v>-3.4872</v>
       </c>
       <c r="G21" t="n">
         <v>-5.3441</v>
@@ -2092,13 +2092,13 @@
         <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8782</v>
+        <v>-0.5956</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3548</v>
+        <v>-0.1526</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5234</v>
+        <v>-0.4431</v>
       </c>
       <c r="V21" t="n">
         <v>0.1554</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.3086</v>
+        <v>-6.4392</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.76</v>
+        <v>-2.6478</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.5485</v>
+        <v>-3.7914</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5472</v>
@@ -2170,13 +2170,13 @@
         <v>1.9534</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3475</v>
+        <v>-0.478</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6849</v>
+        <v>0.4273</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.6625</v>
+        <v>-0.9053</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4373</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.888600000000002</v>
+        <v>-6.1922</v>
       </c>
       <c r="E23" t="n">
-        <v>6.375900000000001</v>
+        <v>6.375799999999998</v>
       </c>
       <c r="F23" t="n">
-        <v>-15.2643</v>
+        <v>-12.5679</v>
       </c>
       <c r="G23" t="n">
-        <v>-9.137800000000002</v>
+        <v>-9.1378</v>
       </c>
       <c r="H23" t="n">
         <v>-11.159</v>
@@ -2224,7 +2224,7 @@
         <v>1.573500000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.477900000000001</v>
+        <v>-2.4779</v>
       </c>
       <c r="L23" t="n">
         <v>4.051499999999999</v>
@@ -2239,7 +2239,7 @@
         <v>-2.0302</v>
       </c>
       <c r="P23" t="n">
-        <v>2.930199999999999</v>
+        <v>2.9302</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.767099999999999</v>
@@ -2248,13 +2248,13 @@
         <v>12.6972</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9077000000000002</v>
+        <v>1.7887</v>
       </c>
       <c r="T23" t="n">
-        <v>4.265899999999999</v>
+        <v>4.2657</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.1737</v>
+        <v>-2.4772</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7732</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484236_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484236_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-0.7312</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1942</v>
+        <v>1.221</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6534</v>
+        <v>1.221</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4592</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6894</v>
+        <v>1.221</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0537</v>
+        <v>0.614</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3644</v>
+        <v>0.607</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6995</v>
+        <v>1.221</v>
       </c>
       <c r="K6" t="n">
-        <v>1.659</v>
+        <v>0.614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0101</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3948</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4049</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0407</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9307</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +985,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9853</v>
+        <v>0.8872</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8796</v>
+        <v>1.3465</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8649</v>
+        <v>-0.4592</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0166</v>
+        <v>1.3824</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7786999999999999</v>
+        <v>1.7468</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7953</v>
+        <v>-0.3644</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2103</v>
+        <v>1.3925</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1241</v>
+        <v>1.352</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3344</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1938</v>
+        <v>-0.0101</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.3948</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5391</v>
+        <v>-0.4049</v>
       </c>
       <c r="P7" t="n">
         <v>-0.1953</v>
@@ -1000,28 +1030,33 @@
         <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0214</v>
+        <v>1.0407</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0888</v>
+        <v>0.9307</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1102</v>
+        <v>0.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2186</v>
+        <v>-1.3405</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.3405</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2024</v>
+        <v>0.307</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7155</v>
+        <v>0.307</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9177999999999999</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0586</v>
+        <v>0.307</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1796</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0408</v>
+        <v>0.307</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5935</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5527</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0994</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7731</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6737</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1438</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4327</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5765</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7675</v>
+        <v>-0.2024</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.389</v>
+        <v>0.7155</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3785</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3919</v>
+        <v>-0.0586</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1456</v>
+        <v>-0.1796</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5375</v>
+        <v>0.121</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5727</v>
+        <v>0.0408</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0205</v>
+        <v>0.5935</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.5527</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8192</v>
+        <v>-0.0994</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1251</v>
+        <v>-0.7731</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9443</v>
+        <v>0.6737</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3756</v>
+        <v>-0.1438</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0935</v>
+        <v>0.4327</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2821</v>
+        <v>-0.5765</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0024</v>
+        <v>-0.2356</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8662</v>
+        <v>-2.1006</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1362</v>
+        <v>1.8649</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6089</v>
+        <v>-1.2375</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8788</v>
+        <v>0.1648</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2698</v>
+        <v>-1.4023</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6488</v>
+        <v>-2.4313</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3239</v>
+        <v>-0.4899</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6751</v>
+        <v>-1.9414</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0399</v>
+        <v>1.1938</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4452</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4052</v>
+        <v>0.5391</v>
       </c>
       <c r="P10" t="n">
         <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9795</v>
+        <v>-0.0214</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0453</v>
+        <v>0.0888</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9342</v>
+        <v>-0.1102</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2186</v>
+        <v>1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SOLE MORGADO</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9008</v>
+        <v>-1.7675</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4649</v>
+        <v>-0.389</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.436</v>
+        <v>-1.3785</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9709</v>
+        <v>-1.3919</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0108</v>
+        <v>0.1456</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9816</v>
+        <v>-1.5375</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0956</v>
+        <v>-0.5727</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6536</v>
+        <v>0.0205</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.442</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1247</v>
+        <v>-0.8192</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6644</v>
+        <v>0.1251</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5397</v>
+        <v>-0.9443</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5895</v>
+        <v>-0.3756</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1739</v>
+        <v>-0.0935</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4155</v>
+        <v>-0.2821</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3405</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3405</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.1149</v>
+        <v>-3.0024</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.1709</v>
+        <v>-1.8662</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.944</v>
+        <v>-1.1362</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.3072</v>
+        <v>-0.6089</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.3252</v>
+        <v>-0.8788</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.982</v>
+        <v>0.2698</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.7988</v>
+        <v>-0.6488</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.1661</v>
+        <v>-1.3239</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6326000000000001</v>
+        <v>0.6751</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5085</v>
+        <v>0.0399</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1591</v>
+        <v>0.4452</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3494</v>
+        <v>-0.4052</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2909</v>
+        <v>-0.9795</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7766999999999999</v>
+        <v>-0.0453</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4858</v>
+        <v>-0.9342</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1219</v>
+        <v>-1.2186</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1219</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. SOLE MORGADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,229 +1483,240 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.40160000000001</v>
+        <v>-3.9008</v>
       </c>
       <c r="E13" t="n">
-        <v>16.7773</v>
+        <v>-2.4649</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.375800000000001</v>
+        <v>-1.436</v>
       </c>
       <c r="G13" t="n">
-        <v>9.137800000000004</v>
+        <v>-1.9709</v>
       </c>
       <c r="H13" t="n">
-        <v>11.159</v>
+        <v>0.0108</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.0213</v>
+        <v>-1.9816</v>
       </c>
       <c r="J13" t="n">
-        <v>10.7114</v>
+        <v>-2.0956</v>
       </c>
       <c r="K13" t="n">
-        <v>8.6812</v>
+        <v>-0.6536</v>
       </c>
       <c r="L13" t="n">
-        <v>2.0303</v>
+        <v>-1.442</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5736</v>
+        <v>0.1247</v>
       </c>
       <c r="N13" t="n">
-        <v>2.478</v>
+        <v>0.6644</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.0515</v>
+        <v>-0.5397</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.9299</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6973</v>
+        <v>-0.1953</v>
       </c>
       <c r="R13" t="n">
-        <v>9.767299999999999</v>
+        <v>0.1953</v>
       </c>
       <c r="S13" t="n">
-        <v>2.420899999999999</v>
+        <v>-0.5895</v>
       </c>
       <c r="T13" t="n">
-        <v>6.6868</v>
+        <v>-0.1739</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.2658</v>
+        <v>-0.4155</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7731</v>
+        <v>-1.3405</v>
       </c>
       <c r="W13" t="n">
-        <v>12.0765</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.3035</v>
+        <v>-1.3405</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7053</v>
+        <v>-7.1149</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5186</v>
+        <v>-6.1709</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1867</v>
+        <v>-0.944</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9677</v>
+        <v>-6.3072</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2269</v>
+        <v>-4.3252</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7408</v>
+        <v>-1.982</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7231</v>
+        <v>-4.7988</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5208</v>
+        <v>-4.1661</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2023</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2446</v>
+        <v>-1.5085</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2939</v>
+        <v>-0.1591</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5385</v>
+        <v>-1.3494</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7581</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3785</v>
+        <v>0.2909</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7954</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5831</v>
+        <v>-0.4858</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3991</v>
+        <v>-0.1219</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3991</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. YUSTE MALO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>TQ-CB PRAT</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6009</v>
+        <v>10.4017</v>
       </c>
       <c r="E15" t="n">
-        <v>6.3292</v>
+        <v>16.7774</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-6.375800000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>6.685</v>
+        <v>9.137900000000004</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.6616</v>
+        <v>11.1592</v>
       </c>
       <c r="I15" t="n">
-        <v>9.3466</v>
+        <v>-2.0213</v>
       </c>
       <c r="J15" t="n">
-        <v>6.7752</v>
+        <v>10.7114</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.5723</v>
+        <v>8.6812</v>
       </c>
       <c r="L15" t="n">
-        <v>9.3476</v>
+        <v>2.0303</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0902</v>
+        <v>-1.5736</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0893</v>
+        <v>2.478</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.001</v>
+        <v>-4.0515</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.3441</v>
+        <v>-2.9299</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9069</v>
+        <v>-12.6973</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>9.767299999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3735</v>
+        <v>2.420899999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.137</v>
+        <v>6.686800000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2365</v>
+        <v>-4.2658</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8865</v>
+        <v>1.7731</v>
       </c>
       <c r="W15" t="n">
-        <v>3.3238</v>
+        <v>12.0765</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.4373</v>
-      </c>
+        <v>-10.3035</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1755</v>
+        <v>5.7053</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2386</v>
+        <v>3.5186</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.0631</v>
+        <v>2.1867</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2924</v>
+        <v>1.9677</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6163</v>
+        <v>1.2269</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3239</v>
+        <v>0.7408</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9539</v>
+        <v>1.7231</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3331</v>
+        <v>1.5208</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6208</v>
+        <v>0.2023</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6615</v>
+        <v>0.2446</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7168</v>
+        <v>-0.2939</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9447</v>
+        <v>0.5385</v>
       </c>
       <c r="P16" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0785</v>
+        <v>2.3785</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8242</v>
+        <v>1.7954</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7457</v>
+        <v>0.5831</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2186</v>
+        <v>-0.3991</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>D. YUSTE MALO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5446</v>
+        <v>5.6009</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.0873</v>
+        <v>6.3292</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5427</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4365</v>
+        <v>6.685</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3313</v>
+        <v>-2.6616</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1052</v>
+        <v>9.3466</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.9511</v>
+        <v>6.7752</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.0374</v>
+        <v>-2.5723</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9137</v>
+        <v>9.3476</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5145999999999999</v>
+        <v>-0.0902</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2939</v>
+        <v>-0.0893</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8085</v>
+        <v>-0.001</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4045</v>
+        <v>0.3735</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2312</v>
+        <v>0.137</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1732</v>
+        <v>0.2365</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4875</v>
+        <v>0.8865</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6093</v>
+        <v>3.3238</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1219</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5498</v>
+        <v>1.8685</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8733</v>
+        <v>4.9316</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.423</v>
+        <v>-3.0631</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6464</v>
+        <v>-0.0146</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2812</v>
+        <v>0.3093</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3652</v>
+        <v>-0.3239</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5696</v>
+        <v>2.6469</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2802</v>
+        <v>2.0261</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8498</v>
+        <v>0.6208</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.216</v>
+        <v>-2.6615</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.001</v>
+        <v>-1.7168</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.215</v>
+        <v>-0.9447</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4437</v>
+        <v>0.0785</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3036</v>
+        <v>0.8242</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8599</v>
+        <v>-0.7457</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2333</v>
+        <v>0.307</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8677</v>
+        <v>0.307</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6344</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5028</v>
+        <v>0.307</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.9878</v>
+        <v>0.307</v>
       </c>
       <c r="I19" t="n">
-        <v>0.485</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.5528</v>
+        <v>0.307</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.6337</v>
+        <v>0.307</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.354</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4041</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1128</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3149</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2021</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3991</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3991</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5133</v>
+        <v>-1.5446</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0746</v>
+        <v>-3.0873</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4387</v>
+        <v>1.5427</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6059</v>
+        <v>-2.4365</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5674</v>
+        <v>-1.3313</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0385</v>
+        <v>-1.1052</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3077</v>
+        <v>-2.9511</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6741</v>
+        <v>-1.0374</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.9137</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2982</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8933</v>
+        <v>-0.2939</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4049</v>
+        <v>0.8085</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7036</v>
+        <v>0.4045</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0145</v>
+        <v>0.2312</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7181</v>
+        <v>0.1732</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2102</v>
+        <v>0.4875</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0084</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3937</v>
+        <v>-1.5498</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9065</v>
+        <v>1.8733</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4872</v>
+        <v>-3.423</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.3441</v>
+        <v>-2.6464</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.4582</v>
+        <v>-2.2812</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.8859</v>
+        <v>-0.3652</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.4917</v>
+        <v>0.5696</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8762</v>
+        <v>-0.2802</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.6155</v>
+        <v>0.8498</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8524</v>
+        <v>-3.216</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.582</v>
+        <v>-2.001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2704</v>
+        <v>-1.215</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5956</v>
+        <v>0.4437</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1526</v>
+        <v>1.3036</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4431</v>
+        <v>-0.8599</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1554</v>
+        <v>-1.4959</v>
       </c>
       <c r="W21" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5591</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.4392</v>
+        <v>-2.2333</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6478</v>
+        <v>-2.8677</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.7914</v>
+        <v>0.6344</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5472</v>
+        <v>-2.5028</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2853</v>
+        <v>-2.9878</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8324</v>
+        <v>0.485</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.145</v>
+        <v>-2.5528</v>
       </c>
       <c r="K22" t="n">
-        <v>1.7421</v>
+        <v>-2.6337</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.8871</v>
+        <v>0.0809</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.4022</v>
+        <v>0.05</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4569</v>
+        <v>-0.354</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9453</v>
+        <v>0.4041</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.478</v>
+        <v>-0.1128</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4273</v>
+        <v>-0.3149</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9053</v>
+        <v>0.2021</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.4373</v>
+        <v>-0.3991</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4373</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,318 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-2.5133</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.0746</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.4387</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.6059</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.5674</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.0385</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.2982</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.8933</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.4049</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.7036</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.7181</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2102</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.0084</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>M. BATALLER LOPEZ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-5.3937</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.9065</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-3.4872</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-5.3441</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.4582</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-2.8859</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-3.4917</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.8762</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-2.6155</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.8524</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.582</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.2704</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.5956</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.1526</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.4431</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.1554</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.7145</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-2.5591</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A. MONTAGUT PUNTI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-6.4392</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.6478</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-3.7914</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.5472</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.8324</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.145</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.7421</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.8871</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.4022</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.4569</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.9453</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.478</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.9053</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484236_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>-6.1922</v>
       </c>
-      <c r="E23" t="n">
-        <v>6.375799999999998</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E26" t="n">
+        <v>6.375800000000002</v>
+      </c>
+      <c r="F26" t="n">
         <v>-12.5679</v>
       </c>
-      <c r="G23" t="n">
-        <v>-9.1378</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="G26" t="n">
+        <v>-9.137800000000002</v>
+      </c>
+      <c r="H26" t="n">
         <v>-11.159</v>
       </c>
-      <c r="I23" t="n">
-        <v>2.021300000000001</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="I26" t="n">
+        <v>2.021300000000002</v>
+      </c>
+      <c r="J26" t="n">
         <v>1.573500000000001</v>
       </c>
-      <c r="K23" t="n">
-        <v>-2.4779</v>
-      </c>
-      <c r="L23" t="n">
-        <v>4.051499999999999</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="K26" t="n">
+        <v>-2.477900000000001</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4.0515</v>
+      </c>
+      <c r="M26" t="n">
         <v>-10.7113</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N26" t="n">
         <v>-8.681100000000001</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O26" t="n">
         <v>-2.0302</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P26" t="n">
         <v>2.9302</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q26" t="n">
         <v>-9.767099999999999</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>12.6972</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S26" t="n">
         <v>1.7887</v>
       </c>
-      <c r="T23" t="n">
-        <v>4.2657</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="T26" t="n">
+        <v>4.265700000000001</v>
+      </c>
+      <c r="U26" t="n">
         <v>-2.4772</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V26" t="n">
         <v>-1.7732</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W26" t="n">
         <v>10.3035</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X26" t="n">
         <v>-12.0767</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
